--- a/data/trans_orig/IP2906_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45278</t>
+          <t>45434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62134</t>
+          <t>62551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38734</t>
+          <t>37506</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65418</t>
+          <t>65013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89388</t>
+          <t>89570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120951</t>
+          <t>121898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50924</t>
+          <t>50507</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67780</t>
+          <t>67624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70933</t>
+          <t>71338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97617</t>
+          <t>98845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128458</t>
+          <t>127511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160021</t>
+          <t>159839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60568</t>
+          <t>60304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85233</t>
+          <t>84444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85582</t>
+          <t>87133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116120</t>
+          <t>116236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155530</t>
+          <t>153628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191660</t>
+          <t>193593</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99052</t>
+          <t>99841</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123717</t>
+          <t>123981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130286</t>
+          <t>130170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160824</t>
+          <t>159273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>239031</t>
+          <t>237098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>275161</t>
+          <t>277063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,33%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64280</t>
+          <t>63389</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88643</t>
+          <t>87848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70529</t>
+          <t>70461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99502</t>
+          <t>97474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140688</t>
+          <t>140757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176133</t>
+          <t>176698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71405</t>
+          <t>72200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95768</t>
+          <t>96659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81654</t>
+          <t>83682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110627</t>
+          <t>110695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165071</t>
+          <t>164506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200516</t>
+          <t>200447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55750</t>
+          <t>55304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77578</t>
+          <t>76207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67241</t>
+          <t>67899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91403</t>
+          <t>92536</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129270</t>
+          <t>131074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161655</t>
+          <t>164606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82806</t>
+          <t>84177</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104634</t>
+          <t>105080</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83729</t>
+          <t>82596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107891</t>
+          <t>107233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173861</t>
+          <t>170910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206246</t>
+          <t>204442</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>246961</t>
+          <t>247107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290031</t>
+          <t>288013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289224</t>
+          <t>290695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343369</t>
+          <t>342775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>543972</t>
+          <t>551504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>617390</t>
+          <t>619270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327744</t>
+          <t>329762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>370814</t>
+          <t>370668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>395675</t>
+          <t>396269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>449820</t>
+          <t>448349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>739430</t>
+          <t>737550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>805316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2906_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49981</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37953</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60816</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,98%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>53756</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45434</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>62551</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>47,55%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>55652</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>46925</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>64127</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>47,67%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>40,19%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>52209</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>37506</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>65013</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,29%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>27,51%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>105965</t>
+          <t>105633</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89570</t>
+          <t>90989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121898</t>
+          <t>119188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72508</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61673</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84536</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>59,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,02%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>59302</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50507</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67624</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>52,45%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>61093</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>52618</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69820</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>52,33%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>45,07%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>59,81%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>84142</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>71338</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>98845</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>61,71%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>52,32%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>72,49%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>188</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>143444</t>
+          <t>133601</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127511</t>
+          <t>120046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159839</t>
+          <t>148245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122489</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122489</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122489</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>113058</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>113058</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>113058</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>116745</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>116745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>116745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>249409</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>249409</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>249409</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>94378</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>80160</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>108688</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,84%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>72719</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>60304</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>84444</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>39,46%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100241</t>
+          <t>73625</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87133</t>
+          <t>62767</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116236</t>
+          <t>85778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172960</t>
+          <t>168004</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153628</t>
+          <t>150724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193593</t>
+          <t>186659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>135706</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>121396</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>149924</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>111566</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99841</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>123981</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>60,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>146165</t>
+          <t>104955</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130170</t>
+          <t>92802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159273</t>
+          <t>115813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>257731</t>
+          <t>240661</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237098</t>
+          <t>222006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>277063</t>
+          <t>257941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>230084</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>230084</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>230084</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>184285</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>184285</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>184285</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>246406</t>
+          <t>178580</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>246406</t>
+          <t>178580</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>246406</t>
+          <t>178580</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>430691</t>
+          <t>408665</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>430691</t>
+          <t>408665</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>430691</t>
+          <t>408665</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75564</t>
+          <t>79325</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63389</t>
+          <t>66382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87848</t>
+          <t>92192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>73104</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>62627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97474</t>
+          <t>84108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>159434</t>
+          <t>152429</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140757</t>
+          <t>135640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176698</t>
+          <t>167381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85332</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72465</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>98275</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>51,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>84484</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>72200</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>96659</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>52,79%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>60,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>97285</t>
+          <t>77830</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83682</t>
+          <t>66826</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110695</t>
+          <t>88307</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>181770</t>
+          <t>163162</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164506</t>
+          <t>148210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200447</t>
+          <t>179951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>160048</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>160048</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>160048</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>150934</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>150934</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>150934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>341204</t>
+          <t>315591</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>341204</t>
+          <t>315591</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>341204</t>
+          <t>315591</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>74763</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>64935</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>86752</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>66283</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>55304</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>76207</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>41,33%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>47,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>79220</t>
+          <t>63925</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67899</t>
+          <t>54272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92536</t>
+          <t>74786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>145503</t>
+          <t>138688</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131074</t>
+          <t>124416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164606</t>
+          <t>154024</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>89347</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77358</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>99175</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>94101</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>84177</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>105080</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>58,67%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>52,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>95912</t>
+          <t>95730</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82596</t>
+          <t>84869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107233</t>
+          <t>105383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>190013</t>
+          <t>185077</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170910</t>
+          <t>169741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204442</t>
+          <t>199349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,57%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164110</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164110</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164110</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>160384</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>160384</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>160384</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>335516</t>
+          <t>323765</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>335516</t>
+          <t>323765</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>335516</t>
+          <t>323765</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>298448</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>269880</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>323279</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>401</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>268322</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>247107</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>288013</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>315541</t>
+          <t>266306</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290695</t>
+          <t>245993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>342775</t>
+          <t>285743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>583863</t>
+          <t>564755</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>551504</t>
+          <t>533428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>619270</t>
+          <t>595068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>382893</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>358062</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>411461</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>56,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52,55%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>60,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>349453</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>329762</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>370668</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>423503</t>
+          <t>339608</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>396269</t>
+          <t>320171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>448349</t>
+          <t>359921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>772957</t>
+          <t>722500</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>737550</t>
+          <t>692187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>805316</t>
+          <t>753827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>905</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>617775</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>617775</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>617775</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605914</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1356820</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1356820</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1356820</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
